--- a/endpoint_excels/iss__history__engines__stock__totals__boards__board__securities__security.xlsx
+++ b/endpoint_excels/iss__history__engines__stock__totals__boards__board__securities__security.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="security" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="security.cursor" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="security.dates" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COLUMN_DOCS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,16 +31,26 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -53,14 +64,34 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -136,6 +167,45 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TBL_02_iss__history__engi" displayName="TBL_02_iss__history__engi" ref="A1:E5" headerRowCount="1">
+  <autoFilter ref="A1:E5"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="SECID"/>
+    <tableColumn id="2" name="REQUEST_URL"/>
+    <tableColumn id="3" name="INDEX"/>
+    <tableColumn id="4" name="TOTAL"/>
+    <tableColumn id="5" name="PAGESIZE"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TBL_03_iss__history__engi" displayName="TBL_03_iss__history__engi" ref="A1:D5" headerRowCount="1">
+  <autoFilter ref="A1:D5"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="SECID"/>
+    <tableColumn id="2" name="REQUEST_URL"/>
+    <tableColumn id="3" name="from"/>
+    <tableColumn id="4" name="till"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ENDPOINT_COLUMN_DOCS" displayName="ENDPOINT_COLUMN_DOCS" ref="A1:C42" headerRowCount="1">
+  <autoFilter ref="A1:C42"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="SHEET_NAME"/>
+    <tableColumn id="2" name="COLUMN_NAME"/>
+    <tableColumn id="3" name="DESCRIPTION_RU"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -429,8 +499,42 @@
   </sheetPr>
   <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="21" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="25" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="31" max="31"/>
+    <col width="20" customWidth="1" min="32" max="32"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>REQUEST_URL</t>
@@ -605,8 +709,15 @@
   </sheetPr>
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SECID</t>
@@ -634,91 +745,94 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/AUCT/securities/SU26238RMFS4.json</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/PACT/securities/SU26238RMFS4.json</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="2" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/TQOB/securities/SU26238RMFS4.json</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="2" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/TQCB/securities/RU000A1041Q0.json</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="2" t="n">
         <v>5000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -730,86 +844,831 @@
   </sheetPr>
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SECID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>REQUEST_URL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>till</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/AUCT/securities/SU26238RMFS4.json</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/PACT/securities/SU26238RMFS4.json</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/TQOB/securities/SU26238RMFS4.json</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>RU000A1041Q0</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/TQCB/securities/RU000A1041Q0.json</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>SHEET_NAME</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>COLUMN_NAME</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DESCRIPTION_RU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>REQUEST_URL</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>URL endpoint ISS, откуда получены данные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
           <t>SECID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Код финансового инструмента (ценной бумаги) в ISS MOEX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>TRADEDATE</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>BOARDID</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Идентификатор торгового режима/доски.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>CURRENCYID</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Код валюты расчётов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>WAPRICE</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>MARKETPRICE2</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>ADMITTEDQUOTE</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>TRENDCLOSE</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>TRENDWAP</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>TRENDWAPPR</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>VOLUME</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>NUMTRADES</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>OPENVAL</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>CLOSEVAL</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>ISSUESIZE</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>FACEVALUE</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Номинальная стоимость бумаги.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>DAILYCAPITALIZATION</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>MONTHLYCAPITALIZATION</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>MP2VALTRD</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>ADMITTEDVALUE</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>MARKETPRICE3</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>MARKETPRICE3TRADESVALUE</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>LISTNAME</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>SYSTIME</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>TRADINGSESSION</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>TRADE_SESSION_DATE</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>security.cursor</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>SECID</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Код финансового инструмента (ценной бумаги) в ISS MOEX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>security.cursor</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>REQUEST_URL</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>URL endpoint ISS, откуда получены данные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>security.cursor</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>INDEX</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>security.cursor</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>security.cursor</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>PAGESIZE</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>security.dates</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>SECID</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Код финансового инструмента (ценной бумаги) в ISS MOEX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>security.dates</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>REQUEST_URL</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>URL endpoint ISS, откуда получены данные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>security.dates</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>security.dates</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>till</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/AUCT/securities/SU26238RMFS4.json</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/PACT/securities/SU26238RMFS4.json</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/TQOB/securities/SU26238RMFS4.json</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>RU000A1041Q0</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/TQCB/securities/RU000A1041Q0.json</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/endpoint_excels/iss__history__engines__stock__totals__boards__board__securities__security.xlsx
+++ b/endpoint_excels/iss__history__engines__stock__totals__boards__board__securities__security.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,16 +30,26 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -53,14 +63,31 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -136,6 +163,33 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TBL_02_iss__history__engi" displayName="TBL_02_iss__history__engi" ref="A1:E5" headerRowCount="1">
+  <autoFilter ref="A1:E5"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="SECID"/>
+    <tableColumn id="2" name="REQUEST_URL"/>
+    <tableColumn id="3" name="INDEX"/>
+    <tableColumn id="4" name="TOTAL"/>
+    <tableColumn id="5" name="PAGESIZE"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TBL_03_iss__history__engi" displayName="TBL_03_iss__history__engi" ref="A1:D5" headerRowCount="1">
+  <autoFilter ref="A1:D5"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="SECID"/>
+    <tableColumn id="2" name="REQUEST_URL"/>
+    <tableColumn id="3" name="from"/>
+    <tableColumn id="4" name="till"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -429,8 +483,42 @@
   </sheetPr>
   <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="21" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="25" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="31" max="31"/>
+    <col width="20" customWidth="1" min="32" max="32"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>REQUEST_URL</t>
@@ -605,8 +693,15 @@
   </sheetPr>
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SECID</t>
@@ -634,91 +729,94 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/AUCT/securities/SU26238RMFS4.json</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/PACT/securities/SU26238RMFS4.json</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="2" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/TQOB/securities/SU26238RMFS4.json</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="2" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/TQCB/securities/RU000A1041Q0.json</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="2" t="n">
         <v>5000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -730,8 +828,14 @@
   </sheetPr>
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SECID</t>
@@ -754,62 +858,65 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/AUCT/securities/SU26238RMFS4.json</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/PACT/securities/SU26238RMFS4.json</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/TQOB/securities/SU26238RMFS4.json</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/history/engines/stock/totals/boards/TQCB/securities/RU000A1041Q0.json</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>